--- a/htr-FHIR/ig/StructureDefinition-fr-information-recipient-extension.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-information-recipient-extension.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T16:07:16+00:00</t>
+    <t>2025-03-06T10:23:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-information-recipient-extension.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-information-recipient-extension.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T10:23:19+00:00</t>
+    <t>2025-03-10T13:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -377,7 +377,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-core-participation-type</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-doc-participation-type</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -768,7 +768,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="77.35546875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="76.63671875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/htr-FHIR/ig/StructureDefinition-fr-information-recipient-extension.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-information-recipient-extension.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-10T13:00:25+00:00</t>
+    <t>2025-03-11T15:29:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -377,7 +377,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-doc-participation-type</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-doc-vs-participation-type</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -768,7 +768,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="76.63671875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="79.3359375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/htr-FHIR/ig/StructureDefinition-fr-information-recipient-extension.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-information-recipient-extension.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T15:29:00+00:00</t>
+    <t>2025-03-12T13:18:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
